--- a/05_Figures/F06_prediction/proteins/training/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_fcsa_II/spls/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="215">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="222">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -140,6 +140,9 @@
     <t xml:space="preserve">CUL2</t>
   </si>
   <si>
+    <t xml:space="preserve">FSCN1</t>
+  </si>
+  <si>
     <t xml:space="preserve">GATD3B</t>
   </si>
   <si>
@@ -152,43 +155,46 @@
     <t xml:space="preserve">LYPLA2</t>
   </si>
   <si>
+    <t xml:space="preserve">MRPL22</t>
+  </si>
+  <si>
     <t xml:space="preserve">MT-ND1</t>
   </si>
   <si>
     <t xml:space="preserve">NDUFS4</t>
   </si>
   <si>
+    <t xml:space="preserve">TUBB2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LAMTOR3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PSAPL1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SH3BGRL3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SNX5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMEM205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRIP2</t>
+  </si>
+  <si>
     <t xml:space="preserve">RTN3</t>
   </si>
   <si>
-    <t xml:space="preserve">SNX5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMEM205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TUBB2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FSCN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LAMTOR3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRPL22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PSAPL1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASPH</t>
+    <t xml:space="preserve">S100A1</t>
   </si>
   <si>
     <t xml:space="preserve">STK38</t>
@@ -197,297 +203,288 @@
     <t xml:space="preserve">UFD1</t>
   </si>
   <si>
+    <t xml:space="preserve">CKMT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HSPB8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAP3K20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NDUFB9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANP32A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CBR4</t>
+  </si>
+  <si>
     <t xml:space="preserve">COX20</t>
   </si>
   <si>
-    <t xml:space="preserve">CRIP2</t>
+    <t xml:space="preserve">OGDH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATP6V1H</t>
   </si>
   <si>
     <t xml:space="preserve">ERGIC1</t>
   </si>
   <si>
-    <t xml:space="preserve">HSPB8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MAP3K20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">S100A1</t>
+    <t xml:space="preserve">PHKA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TSFM</t>
   </si>
   <si>
     <t xml:space="preserve">YARS1</t>
   </si>
   <si>
-    <t xml:space="preserve">CBR4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CKMT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NDUFB9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OGDH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATP6V1H</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TSFM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANP32A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PHKA1</t>
+    <t xml:space="preserve">RAB11B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CD81</t>
   </si>
   <si>
     <t xml:space="preserve">EHD4</t>
   </si>
   <si>
-    <t xml:space="preserve">ACTR1A</t>
+    <t xml:space="preserve">SGCA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SMIM4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TLN1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDIA3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PFKM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PGAM1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLGRKT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SLC25A20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHMP2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPT1A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PLIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRKCSH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PRUNE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RPL38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATAD3A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATG3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAMK2B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ELOB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GLOD4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILF2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IPO7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MGST2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">P4HB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PDP1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PPIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SEC23A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYNJ2BP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VPS13C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AARS1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACTR1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ACYP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AKT1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH1L1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ALDH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANK2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANXA2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">API5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">APOOL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ARF6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASPN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BIN3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNB3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CACNG1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDNF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CFL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CISD2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CNDP2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX6B1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COX7A2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPNE3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CSTB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DBT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DDAH2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DHRS7B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DLST</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DPYSL2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DYNC1LI1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ECH1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF2A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EIF4G1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FHOD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FYCO1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDGF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HDHD2</t>
   </si>
   <si>
     <t xml:space="preserve">HECTD1</t>
   </si>
   <si>
+    <t xml:space="preserve">HLA-DRA</t>
+  </si>
+  <si>
     <t xml:space="preserve">HNRNPA3</t>
   </si>
   <si>
-    <t xml:space="preserve">SMIM4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHMP2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PDIA3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PFKM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLGRKT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SGCA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TLN1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CD81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPT1A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PGAM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRKCSH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PRUNE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RAB11B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPL38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SLC25A20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">VPS13C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATG3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CAMK2B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF5B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ELOB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GLOD4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HLA-DRA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IFITM1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILF2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IPO7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MGST2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">P4HB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PLIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">PPIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEC23A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SH3BGRL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SYNJ2BP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AARS1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ACYP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKT1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AKT2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH1L1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ALDH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANK2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ANXA2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARF6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ARHGAP1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ATAD3A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIN3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNB3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CACNG1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDNF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CFL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CISD2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CNDP2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX6B1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">COX7A2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPNE1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPNE3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CSTB</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DBT</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DDAH2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DHRS7B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DLST</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DPYSL2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DYNC1LI1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ECH1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF2A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF3B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EIF4G1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FHOD1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FN3K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FUS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FYCO1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDGF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HDHD2</t>
-  </si>
-  <si>
     <t xml:space="preserve">HNRNPK</t>
   </si>
   <si>
@@ -500,15 +497,15 @@
     <t xml:space="preserve">HSDL1</t>
   </si>
   <si>
-    <t xml:space="preserve">HTRA2</t>
-  </si>
-  <si>
     <t xml:space="preserve">ITGA7</t>
   </si>
   <si>
     <t xml:space="preserve">LDHB</t>
   </si>
   <si>
+    <t xml:space="preserve">LPP</t>
+  </si>
+  <si>
     <t xml:space="preserve">LUM</t>
   </si>
   <si>
@@ -530,6 +527,9 @@
     <t xml:space="preserve">MRPS17</t>
   </si>
   <si>
+    <t xml:space="preserve">MRPS27</t>
+  </si>
+  <si>
     <t xml:space="preserve">MTCH2</t>
   </si>
   <si>
@@ -545,7 +545,10 @@
     <t xml:space="preserve">NGLY1</t>
   </si>
   <si>
-    <t xml:space="preserve">OSBPL1A</t>
+    <t xml:space="preserve">NUBPL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OSTC</t>
   </si>
   <si>
     <t xml:space="preserve">PCCA</t>
@@ -554,9 +557,6 @@
     <t xml:space="preserve">PDLIM1</t>
   </si>
   <si>
-    <t xml:space="preserve">PDP1</t>
-  </si>
-  <si>
     <t xml:space="preserve">PFDN4</t>
   </si>
   <si>
@@ -572,12 +572,18 @@
     <t xml:space="preserve">PITRM1</t>
   </si>
   <si>
+    <t xml:space="preserve">PRKAA2</t>
+  </si>
+  <si>
     <t xml:space="preserve">PRMT5</t>
   </si>
   <si>
     <t xml:space="preserve">PRPSAP2</t>
   </si>
   <si>
+    <t xml:space="preserve">PSMA1</t>
+  </si>
+  <si>
     <t xml:space="preserve">PSMB2</t>
   </si>
   <si>
@@ -623,6 +629,9 @@
     <t xml:space="preserve">SGCD</t>
   </si>
   <si>
+    <t xml:space="preserve">SHMT2</t>
+  </si>
+  <si>
     <t xml:space="preserve">SLC25A12</t>
   </si>
   <si>
@@ -632,6 +641,9 @@
     <t xml:space="preserve">STK38L</t>
   </si>
   <si>
+    <t xml:space="preserve">STT3A</t>
+  </si>
+  <si>
     <t xml:space="preserve">STT3B</t>
   </si>
   <si>
@@ -647,6 +659,12 @@
     <t xml:space="preserve">UBA1</t>
   </si>
   <si>
+    <t xml:space="preserve">UBE2O</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UCHL5</t>
+  </si>
+  <si>
     <t xml:space="preserve">UGGT1</t>
   </si>
   <si>
@@ -657,6 +675,9 @@
   </si>
   <si>
     <t xml:space="preserve">XRCC5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YWHAQ</t>
   </si>
   <si>
     <t xml:space="preserve">ZYX</t>
@@ -1046,16 +1067,16 @@
         <v>14</v>
       </c>
       <c r="F2" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.77443979679336</v>
+        <v>-1.7663794356105</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.687912087912088</v>
+        <v>-0.643956043956044</v>
       </c>
       <c r="J2"/>
       <c r="K2"/>
@@ -1079,29 +1100,21 @@
         <v>14</v>
       </c>
       <c r="F3" t="n">
-        <v>1904</v>
+        <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.77443979679336</v>
+        <v>-1.7663794356105</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.687912087912088</v>
-      </c>
-      <c r="J3" t="n">
-        <v>0.935323383084577</v>
-      </c>
-      <c r="K3" t="n">
-        <v>0.940298507462687</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-0.711024006851729</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0.723396332178738</v>
-      </c>
+        <v>-0.643956043956044</v>
+      </c>
+      <c r="J3"/>
+      <c r="K3"/>
+      <c r="L3"/>
+      <c r="M3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1125,2206 +1138,6 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="n">
-        <v>-0.945733666368618</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.6856023912023</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-2.77246027410405</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s">
-        <v>15</v>
-      </c>
-      <c r="B5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-1.58747636213699</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.105782820892051</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.240579212755302</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
-        <v>15</v>
-      </c>
-      <c r="B8" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" t="n">
-        <v>-0.532157124643873</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B9" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" t="n">
-        <v>-0.735311838701766</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.303373732234976</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
-        <v>15</v>
-      </c>
-      <c r="B11" t="s">
-        <v>16</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.79386711561689</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-0.448647981814129</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s">
-        <v>15</v>
-      </c>
-      <c r="B13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.041882985542318</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14" t="s">
-        <v>16</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-1.13835565607818</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="s">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C15" t="n">
-        <v>-0.470177729035747</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="s">
-        <v>15</v>
-      </c>
-      <c r="B16" t="s">
-        <v>16</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.26638558605874</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>16</v>
-      </c>
-      <c r="C17" t="n">
-        <v>-1.36386178944412</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s">
-        <v>15</v>
-      </c>
-      <c r="B18" t="s">
-        <v>16</v>
-      </c>
-      <c r="C18" t="n">
-        <v>-0.063220836211427</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s">
-        <v>15</v>
-      </c>
-      <c r="B19" t="s">
-        <v>16</v>
-      </c>
-      <c r="C19" t="n">
-        <v>-0.72737717201418</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" t="s">
-        <v>16</v>
-      </c>
-      <c r="C20" t="n">
-        <v>-1.5318010736405</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="s">
-        <v>15</v>
-      </c>
-      <c r="B21" t="s">
-        <v>16</v>
-      </c>
-      <c r="C21" t="n">
-        <v>-1.12415786095293</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
-        <v>15</v>
-      </c>
-      <c r="B22" t="s">
-        <v>16</v>
-      </c>
-      <c r="C22" t="n">
-        <v>-1.54311801158929</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" t="s">
-        <v>16</v>
-      </c>
-      <c r="C23" t="n">
-        <v>-2.28890432063252</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" t="s">
-        <v>16</v>
-      </c>
-      <c r="C24" t="n">
-        <v>-1.20672687785745</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" t="s">
-        <v>16</v>
-      </c>
-      <c r="C25" t="n">
-        <v>-0.321594123161369</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B26" t="s">
-        <v>16</v>
-      </c>
-      <c r="C26" t="n">
-        <v>-0.031466998827383</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s">
-        <v>15</v>
-      </c>
-      <c r="B27" t="s">
-        <v>16</v>
-      </c>
-      <c r="C27" t="n">
-        <v>-0.432625619856853</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s">
-        <v>15</v>
-      </c>
-      <c r="B28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C28" t="n">
-        <v>0.0714887635237729</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="s">
-        <v>15</v>
-      </c>
-      <c r="B29" t="s">
-        <v>16</v>
-      </c>
-      <c r="C29" t="n">
-        <v>-0.641404828353732</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="s">
-        <v>15</v>
-      </c>
-      <c r="B30" t="s">
-        <v>16</v>
-      </c>
-      <c r="C30" t="n">
-        <v>-0.669367549222591</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s">
-        <v>16</v>
-      </c>
-      <c r="C31" t="n">
-        <v>-1.20483618429179</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s">
-        <v>15</v>
-      </c>
-      <c r="B32" t="s">
-        <v>16</v>
-      </c>
-      <c r="C32" t="n">
-        <v>-0.744658085450663</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B33" t="s">
-        <v>16</v>
-      </c>
-      <c r="C33" t="n">
-        <v>-1.02020946126312</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="s">
-        <v>15</v>
-      </c>
-      <c r="B34" t="s">
-        <v>16</v>
-      </c>
-      <c r="C34" t="n">
-        <v>-0.169693139801178</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s">
-        <v>15</v>
-      </c>
-      <c r="B35" t="s">
-        <v>16</v>
-      </c>
-      <c r="C35" t="n">
-        <v>-0.323153792562224</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="s">
-        <v>15</v>
-      </c>
-      <c r="B36" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" t="n">
-        <v>-0.217896856181997</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="s">
-        <v>15</v>
-      </c>
-      <c r="B37" t="s">
-        <v>16</v>
-      </c>
-      <c r="C37" t="n">
-        <v>-0.406817255882028</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="s">
-        <v>15</v>
-      </c>
-      <c r="B38" t="s">
-        <v>16</v>
-      </c>
-      <c r="C38" t="n">
-        <v>-1.66272089741781</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s">
-        <v>15</v>
-      </c>
-      <c r="B39" t="s">
-        <v>16</v>
-      </c>
-      <c r="C39" t="n">
-        <v>0.0364387657492753</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="s">
-        <v>15</v>
-      </c>
-      <c r="B40" t="s">
-        <v>16</v>
-      </c>
-      <c r="C40" t="n">
-        <v>-0.539154778903015</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s">
-        <v>15</v>
-      </c>
-      <c r="B41" t="s">
-        <v>16</v>
-      </c>
-      <c r="C41" t="n">
-        <v>0.296608938899987</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s">
-        <v>15</v>
-      </c>
-      <c r="B42" t="s">
-        <v>16</v>
-      </c>
-      <c r="C42" t="n">
-        <v>-0.571107419517798</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" t="s">
-        <v>16</v>
-      </c>
-      <c r="C43" t="n">
-        <v>-1.12086041806459</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s">
-        <v>15</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44" t="n">
-        <v>-1.68220099237254</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s">
-        <v>15</v>
-      </c>
-      <c r="B45" t="s">
-        <v>16</v>
-      </c>
-      <c r="C45" t="n">
-        <v>-0.511799434934761</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s">
-        <v>15</v>
-      </c>
-      <c r="B46" t="s">
-        <v>16</v>
-      </c>
-      <c r="C46" t="n">
-        <v>-0.338669087980883</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="s">
-        <v>15</v>
-      </c>
-      <c r="B47" t="s">
-        <v>16</v>
-      </c>
-      <c r="C47" t="n">
-        <v>-0.989228960114725</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="s">
-        <v>15</v>
-      </c>
-      <c r="B48" t="s">
-        <v>16</v>
-      </c>
-      <c r="C48" t="n">
-        <v>-0.368185306177709</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="s">
-        <v>15</v>
-      </c>
-      <c r="B49" t="s">
-        <v>16</v>
-      </c>
-      <c r="C49" t="n">
-        <v>-0.593495977363048</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="s">
-        <v>15</v>
-      </c>
-      <c r="B50" t="s">
-        <v>16</v>
-      </c>
-      <c r="C50" t="n">
-        <v>-0.26390530504165</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="s">
-        <v>15</v>
-      </c>
-      <c r="B51" t="s">
-        <v>16</v>
-      </c>
-      <c r="C51" t="n">
-        <v>-0.559655273787511</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>15</v>
-      </c>
-      <c r="B52" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" t="n">
-        <v>-0.402737696875985</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="s">
-        <v>15</v>
-      </c>
-      <c r="B53" t="s">
-        <v>16</v>
-      </c>
-      <c r="C53" t="n">
-        <v>-1.30827777786491</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="s">
-        <v>15</v>
-      </c>
-      <c r="B54" t="s">
-        <v>16</v>
-      </c>
-      <c r="C54" t="n">
-        <v>-0.831618121553324</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s">
-        <v>15</v>
-      </c>
-      <c r="B55" t="s">
-        <v>16</v>
-      </c>
-      <c r="C55" t="n">
-        <v>-0.600363457200802</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="s">
-        <v>15</v>
-      </c>
-      <c r="B56" t="s">
-        <v>16</v>
-      </c>
-      <c r="C56" t="n">
-        <v>-1.02603719117686</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" t="s">
-        <v>16</v>
-      </c>
-      <c r="C57" t="n">
-        <v>-0.93420015966464</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="s">
-        <v>15</v>
-      </c>
-      <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="n">
-        <v>-0.581323935756202</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s">
-        <v>15</v>
-      </c>
-      <c r="B59" t="s">
-        <v>16</v>
-      </c>
-      <c r="C59" t="n">
-        <v>-1.62539551257091</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="s">
-        <v>15</v>
-      </c>
-      <c r="B60" t="s">
-        <v>16</v>
-      </c>
-      <c r="C60" t="n">
-        <v>-1.36635818808815</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="s">
-        <v>15</v>
-      </c>
-      <c r="B61" t="s">
-        <v>16</v>
-      </c>
-      <c r="C61" t="n">
-        <v>0.0635254145310479</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="s">
-        <v>15</v>
-      </c>
-      <c r="B62" t="s">
-        <v>16</v>
-      </c>
-      <c r="C62" t="n">
-        <v>-0.8237707689469</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="s">
-        <v>15</v>
-      </c>
-      <c r="B63" t="s">
-        <v>16</v>
-      </c>
-      <c r="C63" t="n">
-        <v>-0.556381343992027</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s">
-        <v>15</v>
-      </c>
-      <c r="B64" t="s">
-        <v>16</v>
-      </c>
-      <c r="C64" t="n">
-        <v>-1.17568139930973</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s">
-        <v>15</v>
-      </c>
-      <c r="B65" t="s">
-        <v>16</v>
-      </c>
-      <c r="C65" t="n">
-        <v>-0.427826539378424</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s">
-        <v>15</v>
-      </c>
-      <c r="B66" t="s">
-        <v>16</v>
-      </c>
-      <c r="C66" t="n">
-        <v>0.256453505355244</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s">
-        <v>15</v>
-      </c>
-      <c r="B67" t="s">
-        <v>16</v>
-      </c>
-      <c r="C67" t="n">
-        <v>-0.114890096636385</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="s">
-        <v>15</v>
-      </c>
-      <c r="B68" t="s">
-        <v>16</v>
-      </c>
-      <c r="C68" t="n">
-        <v>-0.00605243495284769</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="s">
-        <v>15</v>
-      </c>
-      <c r="B69" t="s">
-        <v>16</v>
-      </c>
-      <c r="C69" t="n">
-        <v>-0.686234685695419</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="s">
-        <v>15</v>
-      </c>
-      <c r="B70" t="s">
-        <v>16</v>
-      </c>
-      <c r="C70" t="n">
-        <v>-1.35560926317404</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="s">
-        <v>15</v>
-      </c>
-      <c r="B71" t="s">
-        <v>16</v>
-      </c>
-      <c r="C71" t="n">
-        <v>-1.24021855727389</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="s">
-        <v>15</v>
-      </c>
-      <c r="B72" t="s">
-        <v>16</v>
-      </c>
-      <c r="C72" t="n">
-        <v>-1.35928546697148</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="s">
-        <v>15</v>
-      </c>
-      <c r="B73" t="s">
-        <v>16</v>
-      </c>
-      <c r="C73" t="n">
-        <v>-1.4014459263627</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>15</v>
-      </c>
-      <c r="B74" t="s">
-        <v>16</v>
-      </c>
-      <c r="C74" t="n">
-        <v>-0.924462760262642</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>15</v>
-      </c>
-      <c r="B75" t="s">
-        <v>16</v>
-      </c>
-      <c r="C75" t="n">
-        <v>-2.19654508156499</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="s">
-        <v>15</v>
-      </c>
-      <c r="B76" t="s">
-        <v>16</v>
-      </c>
-      <c r="C76" t="n">
-        <v>-1.27533214226193</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="s">
-        <v>15</v>
-      </c>
-      <c r="B77" t="s">
-        <v>16</v>
-      </c>
-      <c r="C77" t="n">
-        <v>0.0189847276449266</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="s">
-        <v>15</v>
-      </c>
-      <c r="B78" t="s">
-        <v>16</v>
-      </c>
-      <c r="C78" t="n">
-        <v>-0.521227900707113</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>15</v>
-      </c>
-      <c r="B79" t="s">
-        <v>16</v>
-      </c>
-      <c r="C79" t="n">
-        <v>-1.44916939904975</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s">
-        <v>16</v>
-      </c>
-      <c r="C80" t="n">
-        <v>-1.22309951777518</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>15</v>
-      </c>
-      <c r="B81" t="s">
-        <v>16</v>
-      </c>
-      <c r="C81" t="n">
-        <v>-0.237882156656974</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s">
-        <v>15</v>
-      </c>
-      <c r="B82" t="s">
-        <v>16</v>
-      </c>
-      <c r="C82" t="n">
-        <v>-1.36927515564303</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="s">
-        <v>15</v>
-      </c>
-      <c r="B83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C83" t="n">
-        <v>0.103548620286758</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>15</v>
-      </c>
-      <c r="B84" t="s">
-        <v>16</v>
-      </c>
-      <c r="C84" t="n">
-        <v>0.430828356379624</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>15</v>
-      </c>
-      <c r="B85" t="s">
-        <v>16</v>
-      </c>
-      <c r="C85" t="n">
-        <v>-1.69837334559084</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s">
-        <v>15</v>
-      </c>
-      <c r="B86" t="s">
-        <v>16</v>
-      </c>
-      <c r="C86" t="n">
-        <v>-0.375643906495782</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>15</v>
-      </c>
-      <c r="B87" t="s">
-        <v>16</v>
-      </c>
-      <c r="C87" t="n">
-        <v>-1.33845335433291</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>15</v>
-      </c>
-      <c r="B88" t="s">
-        <v>16</v>
-      </c>
-      <c r="C88" t="n">
-        <v>-1.53599647397966</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>15</v>
-      </c>
-      <c r="B89" t="s">
-        <v>16</v>
-      </c>
-      <c r="C89" t="n">
-        <v>-0.0238495563540693</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s">
-        <v>15</v>
-      </c>
-      <c r="B90" t="s">
-        <v>16</v>
-      </c>
-      <c r="C90" t="n">
-        <v>-0.693591902058343</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>15</v>
-      </c>
-      <c r="B91" t="s">
-        <v>16</v>
-      </c>
-      <c r="C91" t="n">
-        <v>-2.299627538177</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>15</v>
-      </c>
-      <c r="B92" t="s">
-        <v>16</v>
-      </c>
-      <c r="C92" t="n">
-        <v>-0.73697416489396</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s">
-        <v>15</v>
-      </c>
-      <c r="B93" t="s">
-        <v>16</v>
-      </c>
-      <c r="C93" t="n">
-        <v>-0.949687243550404</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>15</v>
-      </c>
-      <c r="B94" t="s">
-        <v>16</v>
-      </c>
-      <c r="C94" t="n">
-        <v>-1.03232523888295</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>15</v>
-      </c>
-      <c r="B95" t="s">
-        <v>16</v>
-      </c>
-      <c r="C95" t="n">
-        <v>0.0787320241919008</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>15</v>
-      </c>
-      <c r="B96" t="s">
-        <v>16</v>
-      </c>
-      <c r="C96" t="n">
-        <v>-1.56491419943</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s">
-        <v>15</v>
-      </c>
-      <c r="B97" t="s">
-        <v>16</v>
-      </c>
-      <c r="C97" t="n">
-        <v>0.744674320463711</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>15</v>
-      </c>
-      <c r="B98" t="s">
-        <v>16</v>
-      </c>
-      <c r="C98" t="n">
-        <v>-0.698407645730008</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>15</v>
-      </c>
-      <c r="B99" t="s">
-        <v>16</v>
-      </c>
-      <c r="C99" t="n">
-        <v>-0.399541020610851</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>15</v>
-      </c>
-      <c r="B100" t="s">
-        <v>16</v>
-      </c>
-      <c r="C100" t="n">
-        <v>-1.15321052768898</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="s">
-        <v>15</v>
-      </c>
-      <c r="B101" t="s">
-        <v>16</v>
-      </c>
-      <c r="C101" t="n">
-        <v>0.409779079742338</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="s">
-        <v>15</v>
-      </c>
-      <c r="B102" t="s">
-        <v>16</v>
-      </c>
-      <c r="C102" t="n">
-        <v>-0.69645462659726</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="s">
-        <v>15</v>
-      </c>
-      <c r="B103" t="s">
-        <v>16</v>
-      </c>
-      <c r="C103" t="n">
-        <v>-2.76866239676135</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="s">
-        <v>15</v>
-      </c>
-      <c r="B104" t="s">
-        <v>16</v>
-      </c>
-      <c r="C104" t="n">
-        <v>-1.62257168549147</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="s">
-        <v>15</v>
-      </c>
-      <c r="B105" t="s">
-        <v>16</v>
-      </c>
-      <c r="C105" t="n">
-        <v>-0.983207831630567</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="s">
-        <v>15</v>
-      </c>
-      <c r="B106" t="s">
-        <v>16</v>
-      </c>
-      <c r="C106" t="n">
-        <v>-0.31216933139653</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="s">
-        <v>15</v>
-      </c>
-      <c r="B107" t="s">
-        <v>16</v>
-      </c>
-      <c r="C107" t="n">
-        <v>-1.14513945034246</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="s">
-        <v>15</v>
-      </c>
-      <c r="B108" t="s">
-        <v>16</v>
-      </c>
-      <c r="C108" t="n">
-        <v>-0.366279760829774</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="s">
-        <v>15</v>
-      </c>
-      <c r="B109" t="s">
-        <v>16</v>
-      </c>
-      <c r="C109" t="n">
-        <v>-0.44068866042528</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="s">
-        <v>15</v>
-      </c>
-      <c r="B110" t="s">
-        <v>16</v>
-      </c>
-      <c r="C110" t="n">
-        <v>-0.330500280166457</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="s">
-        <v>15</v>
-      </c>
-      <c r="B111" t="s">
-        <v>16</v>
-      </c>
-      <c r="C111" t="n">
-        <v>-0.141683588579663</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s">
-        <v>15</v>
-      </c>
-      <c r="B112" t="s">
-        <v>16</v>
-      </c>
-      <c r="C112" t="n">
-        <v>0.217061127072316</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="s">
-        <v>15</v>
-      </c>
-      <c r="B113" t="s">
-        <v>16</v>
-      </c>
-      <c r="C113" t="n">
-        <v>-0.635624914185428</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="s">
-        <v>15</v>
-      </c>
-      <c r="B114" t="s">
-        <v>16</v>
-      </c>
-      <c r="C114" t="n">
-        <v>0.371053186822179</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="s">
-        <v>15</v>
-      </c>
-      <c r="B115" t="s">
-        <v>16</v>
-      </c>
-      <c r="C115" t="n">
-        <v>0.0544049331462533</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="s">
-        <v>15</v>
-      </c>
-      <c r="B116" t="s">
-        <v>16</v>
-      </c>
-      <c r="C116" t="n">
-        <v>-1.86459548004639</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="s">
-        <v>15</v>
-      </c>
-      <c r="B117" t="s">
-        <v>16</v>
-      </c>
-      <c r="C117" t="n">
-        <v>0.195543139007988</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="s">
-        <v>15</v>
-      </c>
-      <c r="B118" t="s">
-        <v>16</v>
-      </c>
-      <c r="C118" t="n">
-        <v>-0.897293289609954</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="s">
-        <v>15</v>
-      </c>
-      <c r="B119" t="s">
-        <v>16</v>
-      </c>
-      <c r="C119" t="n">
-        <v>-3.40260181784977</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="s">
-        <v>15</v>
-      </c>
-      <c r="B120" t="s">
-        <v>16</v>
-      </c>
-      <c r="C120" t="n">
-        <v>-1.29406942508606</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="s">
-        <v>15</v>
-      </c>
-      <c r="B121" t="s">
-        <v>16</v>
-      </c>
-      <c r="C121" t="n">
-        <v>-0.332363073776317</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s">
-        <v>15</v>
-      </c>
-      <c r="B122" t="s">
-        <v>16</v>
-      </c>
-      <c r="C122" t="n">
-        <v>-0.000561539298933988</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="s">
-        <v>15</v>
-      </c>
-      <c r="B123" t="s">
-        <v>16</v>
-      </c>
-      <c r="C123" t="n">
-        <v>-1.0070001124289</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s">
-        <v>15</v>
-      </c>
-      <c r="B124" t="s">
-        <v>16</v>
-      </c>
-      <c r="C124" t="n">
-        <v>-0.200918246501949</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="s">
-        <v>15</v>
-      </c>
-      <c r="B125" t="s">
-        <v>16</v>
-      </c>
-      <c r="C125" t="n">
-        <v>-0.107110036248422</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="s">
-        <v>15</v>
-      </c>
-      <c r="B126" t="s">
-        <v>16</v>
-      </c>
-      <c r="C126" t="n">
-        <v>-0.707889636436349</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="s">
-        <v>15</v>
-      </c>
-      <c r="B127" t="s">
-        <v>16</v>
-      </c>
-      <c r="C127" t="n">
-        <v>-0.093236482903962</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="s">
-        <v>15</v>
-      </c>
-      <c r="B128" t="s">
-        <v>16</v>
-      </c>
-      <c r="C128" t="n">
-        <v>0.564177341127163</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="s">
-        <v>15</v>
-      </c>
-      <c r="B129" t="s">
-        <v>16</v>
-      </c>
-      <c r="C129" t="n">
-        <v>-1.73034533202432</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="s">
-        <v>15</v>
-      </c>
-      <c r="B130" t="s">
-        <v>16</v>
-      </c>
-      <c r="C130" t="n">
-        <v>-0.813807669874913</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="s">
-        <v>15</v>
-      </c>
-      <c r="B131" t="s">
-        <v>16</v>
-      </c>
-      <c r="C131" t="n">
-        <v>-1.5495324617535</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="s">
-        <v>15</v>
-      </c>
-      <c r="B132" t="s">
-        <v>16</v>
-      </c>
-      <c r="C132" t="n">
-        <v>-0.347628549452225</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="s">
-        <v>15</v>
-      </c>
-      <c r="B133" t="s">
-        <v>16</v>
-      </c>
-      <c r="C133" t="n">
-        <v>-0.549828564695754</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="s">
-        <v>15</v>
-      </c>
-      <c r="B134" t="s">
-        <v>16</v>
-      </c>
-      <c r="C134" t="n">
-        <v>-0.383737080840488</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="s">
-        <v>15</v>
-      </c>
-      <c r="B135" t="s">
-        <v>16</v>
-      </c>
-      <c r="C135" t="n">
-        <v>-0.0152424883346214</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="s">
-        <v>15</v>
-      </c>
-      <c r="B136" t="s">
-        <v>16</v>
-      </c>
-      <c r="C136" t="n">
-        <v>-0.491669156993501</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="s">
-        <v>15</v>
-      </c>
-      <c r="B137" t="s">
-        <v>16</v>
-      </c>
-      <c r="C137" t="n">
-        <v>-0.835003074472765</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="s">
-        <v>15</v>
-      </c>
-      <c r="B138" t="s">
-        <v>16</v>
-      </c>
-      <c r="C138" t="n">
-        <v>-1.26024364031952</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="s">
-        <v>15</v>
-      </c>
-      <c r="B139" t="s">
-        <v>16</v>
-      </c>
-      <c r="C139" t="n">
-        <v>-0.514541006337927</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="s">
-        <v>15</v>
-      </c>
-      <c r="B140" t="s">
-        <v>16</v>
-      </c>
-      <c r="C140" t="n">
-        <v>0.105431685339167</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="s">
-        <v>15</v>
-      </c>
-      <c r="B141" t="s">
-        <v>16</v>
-      </c>
-      <c r="C141" t="n">
-        <v>0.02071248973226</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="s">
-        <v>15</v>
-      </c>
-      <c r="B142" t="s">
-        <v>16</v>
-      </c>
-      <c r="C142" t="n">
-        <v>-0.458626498213965</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="s">
-        <v>15</v>
-      </c>
-      <c r="B143" t="s">
-        <v>16</v>
-      </c>
-      <c r="C143" t="n">
-        <v>0.0537924903431554</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="s">
-        <v>15</v>
-      </c>
-      <c r="B144" t="s">
-        <v>16</v>
-      </c>
-      <c r="C144" t="n">
-        <v>-1.19626193578061</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="s">
-        <v>15</v>
-      </c>
-      <c r="B145" t="s">
-        <v>16</v>
-      </c>
-      <c r="C145" t="n">
-        <v>-1.06613858200027</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="s">
-        <v>15</v>
-      </c>
-      <c r="B146" t="s">
-        <v>16</v>
-      </c>
-      <c r="C146" t="n">
-        <v>-1.3792837714648</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="s">
-        <v>15</v>
-      </c>
-      <c r="B147" t="s">
-        <v>16</v>
-      </c>
-      <c r="C147" t="n">
-        <v>-0.6379921216562</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="s">
-        <v>15</v>
-      </c>
-      <c r="B148" t="s">
-        <v>16</v>
-      </c>
-      <c r="C148" t="n">
-        <v>-0.204948165404475</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="s">
-        <v>15</v>
-      </c>
-      <c r="B149" t="s">
-        <v>16</v>
-      </c>
-      <c r="C149" t="n">
-        <v>-0.0433775903189875</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="s">
-        <v>15</v>
-      </c>
-      <c r="B150" t="s">
-        <v>16</v>
-      </c>
-      <c r="C150" t="n">
-        <v>-0.459716723027853</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="s">
-        <v>15</v>
-      </c>
-      <c r="B151" t="s">
-        <v>16</v>
-      </c>
-      <c r="C151" t="n">
-        <v>-0.0961013535314119</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="s">
-        <v>15</v>
-      </c>
-      <c r="B152" t="s">
-        <v>16</v>
-      </c>
-      <c r="C152" t="n">
-        <v>-0.482227049703168</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="s">
-        <v>15</v>
-      </c>
-      <c r="B153" t="s">
-        <v>16</v>
-      </c>
-      <c r="C153" t="n">
-        <v>-0.104263252424947</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="s">
-        <v>15</v>
-      </c>
-      <c r="B154" t="s">
-        <v>16</v>
-      </c>
-      <c r="C154" t="n">
-        <v>-1.55113761317627</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="s">
-        <v>15</v>
-      </c>
-      <c r="B155" t="s">
-        <v>16</v>
-      </c>
-      <c r="C155" t="n">
-        <v>-0.958623399874154</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="s">
-        <v>15</v>
-      </c>
-      <c r="B156" t="s">
-        <v>16</v>
-      </c>
-      <c r="C156" t="n">
-        <v>-1.08825387953883</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="s">
-        <v>15</v>
-      </c>
-      <c r="B157" t="s">
-        <v>16</v>
-      </c>
-      <c r="C157" t="n">
-        <v>-0.700846008463772</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="s">
-        <v>15</v>
-      </c>
-      <c r="B158" t="s">
-        <v>16</v>
-      </c>
-      <c r="C158" t="n">
-        <v>-0.147895374901515</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="s">
-        <v>15</v>
-      </c>
-      <c r="B159" t="s">
-        <v>16</v>
-      </c>
-      <c r="C159" t="n">
-        <v>-0.474479231493146</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="s">
-        <v>15</v>
-      </c>
-      <c r="B160" t="s">
-        <v>16</v>
-      </c>
-      <c r="C160" t="n">
-        <v>-1.71433126863523</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="s">
-        <v>15</v>
-      </c>
-      <c r="B161" t="s">
-        <v>16</v>
-      </c>
-      <c r="C161" t="n">
-        <v>-0.576830153493967</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="s">
-        <v>15</v>
-      </c>
-      <c r="B162" t="s">
-        <v>16</v>
-      </c>
-      <c r="C162" t="n">
-        <v>-1.75152233477358</v>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="s">
-        <v>15</v>
-      </c>
-      <c r="B163" t="s">
-        <v>16</v>
-      </c>
-      <c r="C163" t="n">
-        <v>-2.72889875357763</v>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="s">
-        <v>15</v>
-      </c>
-      <c r="B164" t="s">
-        <v>16</v>
-      </c>
-      <c r="C164" t="n">
-        <v>-0.202926130438884</v>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="s">
-        <v>15</v>
-      </c>
-      <c r="B165" t="s">
-        <v>16</v>
-      </c>
-      <c r="C165" t="n">
-        <v>-0.00814843836742218</v>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="s">
-        <v>15</v>
-      </c>
-      <c r="B166" t="s">
-        <v>16</v>
-      </c>
-      <c r="C166" t="n">
-        <v>-0.718776539817338</v>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="s">
-        <v>15</v>
-      </c>
-      <c r="B167" t="s">
-        <v>16</v>
-      </c>
-      <c r="C167" t="n">
-        <v>-1.48066657644824</v>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="s">
-        <v>15</v>
-      </c>
-      <c r="B168" t="s">
-        <v>16</v>
-      </c>
-      <c r="C168" t="n">
-        <v>0.432479982630141</v>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="s">
-        <v>15</v>
-      </c>
-      <c r="B169" t="s">
-        <v>16</v>
-      </c>
-      <c r="C169" t="n">
-        <v>0.15834190739727</v>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="s">
-        <v>15</v>
-      </c>
-      <c r="B170" t="s">
-        <v>16</v>
-      </c>
-      <c r="C170" t="n">
-        <v>-0.31099100553073</v>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="s">
-        <v>15</v>
-      </c>
-      <c r="B171" t="s">
-        <v>16</v>
-      </c>
-      <c r="C171" t="n">
-        <v>0.0728192888408481</v>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="s">
-        <v>15</v>
-      </c>
-      <c r="B172" t="s">
-        <v>16</v>
-      </c>
-      <c r="C172" t="n">
-        <v>-1.94550274434896</v>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="s">
-        <v>15</v>
-      </c>
-      <c r="B173" t="s">
-        <v>16</v>
-      </c>
-      <c r="C173" t="n">
-        <v>-0.0851185300781916</v>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="s">
-        <v>15</v>
-      </c>
-      <c r="B174" t="s">
-        <v>16</v>
-      </c>
-      <c r="C174" t="n">
-        <v>-0.284688272812251</v>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="s">
-        <v>15</v>
-      </c>
-      <c r="B175" t="s">
-        <v>16</v>
-      </c>
-      <c r="C175" t="n">
-        <v>0.256579708485733</v>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="s">
-        <v>15</v>
-      </c>
-      <c r="B176" t="s">
-        <v>16</v>
-      </c>
-      <c r="C176" t="n">
-        <v>-0.251157169459135</v>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="s">
-        <v>15</v>
-      </c>
-      <c r="B177" t="s">
-        <v>16</v>
-      </c>
-      <c r="C177" t="n">
-        <v>-0.76441101194017</v>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="s">
-        <v>15</v>
-      </c>
-      <c r="B178" t="s">
-        <v>16</v>
-      </c>
-      <c r="C178" t="n">
-        <v>0.318733503085483</v>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="s">
-        <v>15</v>
-      </c>
-      <c r="B179" t="s">
-        <v>16</v>
-      </c>
-      <c r="C179" t="n">
-        <v>-0.338533327144856</v>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="s">
-        <v>15</v>
-      </c>
-      <c r="B180" t="s">
-        <v>16</v>
-      </c>
-      <c r="C180" t="n">
-        <v>0.239744033387996</v>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="s">
-        <v>15</v>
-      </c>
-      <c r="B181" t="s">
-        <v>16</v>
-      </c>
-      <c r="C181" t="n">
-        <v>-0.163802734420129</v>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="s">
-        <v>15</v>
-      </c>
-      <c r="B182" t="s">
-        <v>16</v>
-      </c>
-      <c r="C182" t="n">
-        <v>-0.265074282925889</v>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="s">
-        <v>15</v>
-      </c>
-      <c r="B183" t="s">
-        <v>16</v>
-      </c>
-      <c r="C183" t="n">
-        <v>0.0503075766175921</v>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="s">
-        <v>15</v>
-      </c>
-      <c r="B184" t="s">
-        <v>16</v>
-      </c>
-      <c r="C184" t="n">
-        <v>-1.10148141241106</v>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="s">
-        <v>15</v>
-      </c>
-      <c r="B185" t="s">
-        <v>16</v>
-      </c>
-      <c r="C185" t="n">
-        <v>0.416516788214358</v>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="s">
-        <v>15</v>
-      </c>
-      <c r="B186" t="s">
-        <v>16</v>
-      </c>
-      <c r="C186" t="n">
-        <v>-0.465248300129762</v>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="s">
-        <v>15</v>
-      </c>
-      <c r="B187" t="s">
-        <v>16</v>
-      </c>
-      <c r="C187" t="n">
-        <v>-1.02915477359501</v>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="s">
-        <v>15</v>
-      </c>
-      <c r="B188" t="s">
-        <v>16</v>
-      </c>
-      <c r="C188" t="n">
-        <v>-1.05115505464436</v>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="s">
-        <v>15</v>
-      </c>
-      <c r="B189" t="s">
-        <v>16</v>
-      </c>
-      <c r="C189" t="n">
-        <v>0.344108275036884</v>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="s">
-        <v>15</v>
-      </c>
-      <c r="B190" t="s">
-        <v>16</v>
-      </c>
-      <c r="C190" t="n">
-        <v>-0.951454571844209</v>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="s">
-        <v>15</v>
-      </c>
-      <c r="B191" t="s">
-        <v>16</v>
-      </c>
-      <c r="C191" t="n">
-        <v>-2.09074209147745</v>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="s">
-        <v>15</v>
-      </c>
-      <c r="B192" t="s">
-        <v>16</v>
-      </c>
-      <c r="C192" t="n">
-        <v>-1.0549880753913</v>
-      </c>
-    </row>
-    <row r="193">
-      <c r="A193" t="s">
-        <v>15</v>
-      </c>
-      <c r="B193" t="s">
-        <v>16</v>
-      </c>
-      <c r="C193" t="n">
-        <v>-1.24056335915409</v>
-      </c>
-    </row>
-    <row r="194">
-      <c r="A194" t="s">
-        <v>15</v>
-      </c>
-      <c r="B194" t="s">
-        <v>16</v>
-      </c>
-      <c r="C194" t="n">
-        <v>-0.494932005329755</v>
-      </c>
-    </row>
-    <row r="195">
-      <c r="A195" t="s">
-        <v>15</v>
-      </c>
-      <c r="B195" t="s">
-        <v>16</v>
-      </c>
-      <c r="C195" t="n">
-        <v>-0.935175952882557</v>
-      </c>
-    </row>
-    <row r="196">
-      <c r="A196" t="s">
-        <v>15</v>
-      </c>
-      <c r="B196" t="s">
-        <v>16</v>
-      </c>
-      <c r="C196" t="n">
-        <v>-0.402266809292783</v>
-      </c>
-    </row>
-    <row r="197">
-      <c r="A197" t="s">
-        <v>15</v>
-      </c>
-      <c r="B197" t="s">
-        <v>16</v>
-      </c>
-      <c r="C197" t="n">
-        <v>-0.621631208039353</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="s">
-        <v>15</v>
-      </c>
-      <c r="B198" t="s">
-        <v>16</v>
-      </c>
-      <c r="C198" t="n">
-        <v>-0.447013766499441</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="s">
-        <v>15</v>
-      </c>
-      <c r="B199" t="s">
-        <v>16</v>
-      </c>
-      <c r="C199" t="n">
-        <v>-2.2351460345854</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="s">
-        <v>15</v>
-      </c>
-      <c r="B200" t="s">
-        <v>16</v>
-      </c>
-      <c r="C200" t="n">
-        <v>-1.5055912633694</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="s">
-        <v>15</v>
-      </c>
-      <c r="B201" t="s">
-        <v>16</v>
-      </c>
-      <c r="C201" t="n">
-        <v>-2.27508228877114</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
@@ -3367,7 +1180,7 @@
         <v>517.34</v>
       </c>
       <c r="E2" t="n">
-        <v>-1017.42525597558</v>
+        <v>-1000.18670893863</v>
       </c>
     </row>
     <row r="3">
@@ -3384,7 +1197,7 @@
         <v>1517.85</v>
       </c>
       <c r="E3" t="n">
-        <v>-668.392309243589</v>
+        <v>-644.700480856172</v>
       </c>
     </row>
     <row r="4">
@@ -3401,7 +1214,7 @@
         <v>2790.83</v>
       </c>
       <c r="E4" t="n">
-        <v>-1911.98324107734</v>
+        <v>-1917.66468418095</v>
       </c>
     </row>
     <row r="5">
@@ -3418,7 +1231,7 @@
         <v>739.459999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>624.268065560188</v>
+        <v>473.303885285477</v>
       </c>
     </row>
     <row r="6">
@@ -3435,7 +1248,7 @@
         <v>1179</v>
       </c>
       <c r="E6" t="n">
-        <v>-370.778262881331</v>
+        <v>-389.331547002713</v>
       </c>
     </row>
     <row r="7">
@@ -3452,7 +1265,7 @@
         <v>682.55</v>
       </c>
       <c r="E7" t="n">
-        <v>-2450.15769140869</v>
+        <v>-2429.97682047656</v>
       </c>
     </row>
     <row r="8">
@@ -3469,7 +1282,7 @@
         <v>-171.76</v>
       </c>
       <c r="E8" t="n">
-        <v>1478.01099419362</v>
+        <v>1462.45178737914</v>
       </c>
     </row>
     <row r="9">
@@ -3486,7 +1299,7 @@
         <v>854.04</v>
       </c>
       <c r="E9" t="n">
-        <v>-249.032346437604</v>
+        <v>-198.977945190548</v>
       </c>
     </row>
     <row r="10">
@@ -3503,7 +1316,7 @@
         <v>-1503.6</v>
       </c>
       <c r="E10" t="n">
-        <v>1149.59363628706</v>
+        <v>1177.90902752366</v>
       </c>
     </row>
     <row r="11">
@@ -3520,7 +1333,7 @@
         <v>-88.7199999999993</v>
       </c>
       <c r="E11" t="n">
-        <v>291.458760291771</v>
+        <v>360.17628618088</v>
       </c>
     </row>
     <row r="12">
@@ -3537,7 +1350,7 @@
         <v>-2305.05</v>
       </c>
       <c r="E12" t="n">
-        <v>697.82088936423</v>
+        <v>569.512763258189</v>
       </c>
     </row>
     <row r="13">
@@ -3554,7 +1367,7 @@
         <v>-1179.58</v>
       </c>
       <c r="E13" t="n">
-        <v>-308.443738651061</v>
+        <v>-414.399063352767</v>
       </c>
     </row>
     <row r="14">
@@ -3571,7 +1384,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E14" t="n">
-        <v>873.693705612204</v>
+        <v>877.248935719789</v>
       </c>
     </row>
     <row r="15">
@@ -3588,7 +1401,7 @@
         <v>-1081</v>
       </c>
       <c r="E15" t="n">
-        <v>871.445542920641</v>
+        <v>1058.61071959066</v>
       </c>
     </row>
   </sheetData>
@@ -3851,10 +1664,10 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
-        <v>0.928571428571429</v>
+        <v>0.857142857142857</v>
       </c>
     </row>
     <row r="16">
@@ -3953,10 +1766,10 @@
         <v>56</v>
       </c>
       <c r="D21" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" t="n">
-        <v>0.857142857142857</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="22">
@@ -4021,10 +1834,10 @@
         <v>60</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E25" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="26">
@@ -4038,10 +1851,10 @@
         <v>61</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E26" t="n">
-        <v>0.714285714285714</v>
+        <v>0.785714285714286</v>
       </c>
     </row>
     <row r="27">
@@ -4123,10 +1936,10 @@
         <v>66</v>
       </c>
       <c r="D31" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E31" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="32">
@@ -4140,10 +1953,10 @@
         <v>67</v>
       </c>
       <c r="D32" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E32" t="n">
-        <v>0.714285714285714</v>
+        <v>0.642857142857143</v>
       </c>
     </row>
     <row r="33">
@@ -4208,10 +2021,10 @@
         <v>71</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E36" t="n">
-        <v>0.642857142857143</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="37">
@@ -4259,10 +2072,10 @@
         <v>74</v>
       </c>
       <c r="D39" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E39" t="n">
-        <v>0.5</v>
+        <v>0.571428571428571</v>
       </c>
     </row>
     <row r="40">
@@ -4378,10 +2191,10 @@
         <v>81</v>
       </c>
       <c r="D46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E46" t="n">
-        <v>0.285714285714286</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="47">
@@ -4395,10 +2208,10 @@
         <v>82</v>
       </c>
       <c r="D47" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E47" t="n">
-        <v>0.285714285714286</v>
+        <v>0.357142857142857</v>
       </c>
     </row>
     <row r="48">
@@ -4497,10 +2310,10 @@
         <v>88</v>
       </c>
       <c r="D53" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0.285714285714286</v>
+        <v>0.214285714285714</v>
       </c>
     </row>
     <row r="54">
@@ -4599,10 +2412,10 @@
         <v>94</v>
       </c>
       <c r="D59" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="60">
@@ -4616,10 +2429,10 @@
         <v>95</v>
       </c>
       <c r="D60" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="61">
@@ -4633,10 +2446,10 @@
         <v>96</v>
       </c>
       <c r="D61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="62">
@@ -4650,10 +2463,10 @@
         <v>97</v>
       </c>
       <c r="D62" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
-        <v>0.214285714285714</v>
+        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="63">
@@ -4922,10 +2735,10 @@
         <v>113</v>
       </c>
       <c r="D78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E78" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="79">
@@ -4939,10 +2752,10 @@
         <v>114</v>
       </c>
       <c r="D79" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>0.142857142857143</v>
+        <v>0.0714285714285714</v>
       </c>
     </row>
     <row r="80">
@@ -6642,6 +4455,125 @@
         <v>1</v>
       </c>
       <c r="E179" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="s">
+        <v>215</v>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+      <c r="E180" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="s">
+        <v>216</v>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
+      </c>
+      <c r="E181" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="s">
+        <v>217</v>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
+      </c>
+      <c r="E182" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="s">
+        <v>218</v>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="s">
+        <v>219</v>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="s">
+        <v>220</v>
+      </c>
+      <c r="D185" t="n">
+        <v>1</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="s">
+        <v>221</v>
+      </c>
+      <c r="D186" t="n">
+        <v>1</v>
+      </c>
+      <c r="E186" t="n">
         <v>0.0714285714285714</v>
       </c>
     </row>

--- a/05_Figures/F06_prediction/proteins/training/d_fcsa_II/spls/c_data/results.xlsx
+++ b/05_Figures/F06_prediction/proteins/training/d_fcsa_II/spls/c_data/results.xlsx
@@ -1103,7 +1103,7 @@
         <v>1899</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H3" t="n">
         <v>-1.7663794356105</v>
@@ -1111,10 +1111,18 @@
       <c r="I3" t="n">
         <v>-0.643956043956044</v>
       </c>
-      <c r="J3"/>
-      <c r="K3"/>
-      <c r="L3"/>
-      <c r="M3"/>
+      <c r="J3" t="n">
+        <v>0.915422885572139</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.90547263681592</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.73070030041344</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.72871394970201</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1138,6 +1146,2206 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="n">
+        <v>-0.941670228497838</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.80626745552922</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-2.72222418647411</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-1.88714712555064</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.0642164511537064</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>15</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.172553797347311</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="n">
+        <v>-0.621593175379904</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="n">
+        <v>-0.77164636036767</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="n">
+        <v>-0.214782737802118</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.76937255340583</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-0.439796028440356</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.130958015574926</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-1.12105354547538</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.424519846442171</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.36891125446414</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-1.41026977815412</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.0990338493546921</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>15</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="n">
+        <v>-0.63584479216722</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="n">
+        <v>-1.50427084029613</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>15</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.50868422357462</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>15</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.53621217963928</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>15</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-1.7318054003815</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.5569280877705</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="n">
+        <v>-0.433455211084828</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="n">
+        <v>-0.0326058111783969</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="n">
+        <v>-0.503406505795033</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.063974079460161</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="n">
+        <v>-0.665950969954306</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="n">
+        <v>-0.512910439323056</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>15</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="n">
+        <v>-1.39216710335922</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>15</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="n">
+        <v>-0.790441449999104</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>15</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="n">
+        <v>-0.756802092207746</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="n">
+        <v>-0.169099600206677</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="n">
+        <v>-0.491800477094115</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="n">
+        <v>-0.168488547918705</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="n">
+        <v>-0.839702138989165</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>15</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="n">
+        <v>-1.70951083206375</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="n">
+        <v>-0.0657975141892768</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="n">
+        <v>-0.559987107107314</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>15</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="n">
+        <v>0.321364027257748</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="n">
+        <v>-0.649512016908135</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>15</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="n">
+        <v>-1.17558448502928</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="n">
+        <v>-1.72066476581404</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" t="n">
+        <v>-0.754289973497774</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" t="n">
+        <v>-0.331673160171986</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>15</v>
+      </c>
+      <c r="B47" t="s">
+        <v>16</v>
+      </c>
+      <c r="C47" t="n">
+        <v>-0.947538571896791</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>15</v>
+      </c>
+      <c r="B48" t="s">
+        <v>16</v>
+      </c>
+      <c r="C48" t="n">
+        <v>-0.497439243257781</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>15</v>
+      </c>
+      <c r="B49" t="s">
+        <v>16</v>
+      </c>
+      <c r="C49" t="n">
+        <v>-0.570754976327783</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>15</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="n">
+        <v>-0.476695109567264</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>15</v>
+      </c>
+      <c r="B51" t="s">
+        <v>16</v>
+      </c>
+      <c r="C51" t="n">
+        <v>-0.682002009712166</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>15</v>
+      </c>
+      <c r="B52" t="s">
+        <v>16</v>
+      </c>
+      <c r="C52" t="n">
+        <v>-0.50354824005048</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>15</v>
+      </c>
+      <c r="B53" t="s">
+        <v>16</v>
+      </c>
+      <c r="C53" t="n">
+        <v>-1.87864120711931</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>15</v>
+      </c>
+      <c r="B54" t="s">
+        <v>16</v>
+      </c>
+      <c r="C54" t="n">
+        <v>-0.702405427605601</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>15</v>
+      </c>
+      <c r="B55" t="s">
+        <v>16</v>
+      </c>
+      <c r="C55" t="n">
+        <v>-0.447462984386768</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>15</v>
+      </c>
+      <c r="B56" t="s">
+        <v>16</v>
+      </c>
+      <c r="C56" t="n">
+        <v>-0.950748508642516</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>15</v>
+      </c>
+      <c r="B57" t="s">
+        <v>16</v>
+      </c>
+      <c r="C57" t="n">
+        <v>-1.05550225721831</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>16</v>
+      </c>
+      <c r="C58" t="n">
+        <v>-0.540736425799512</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>15</v>
+      </c>
+      <c r="B59" t="s">
+        <v>16</v>
+      </c>
+      <c r="C59" t="n">
+        <v>-1.50700440636016</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>15</v>
+      </c>
+      <c r="B60" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" t="n">
+        <v>-1.3629224690421</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>15</v>
+      </c>
+      <c r="B61" t="s">
+        <v>16</v>
+      </c>
+      <c r="C61" t="n">
+        <v>-0.160865079837521</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>15</v>
+      </c>
+      <c r="B62" t="s">
+        <v>16</v>
+      </c>
+      <c r="C62" t="n">
+        <v>-1.39490696883493</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>15</v>
+      </c>
+      <c r="B63" t="s">
+        <v>16</v>
+      </c>
+      <c r="C63" t="n">
+        <v>-0.50306005029978</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>15</v>
+      </c>
+      <c r="B64" t="s">
+        <v>16</v>
+      </c>
+      <c r="C64" t="n">
+        <v>-1.14640174850923</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>15</v>
+      </c>
+      <c r="B65" t="s">
+        <v>16</v>
+      </c>
+      <c r="C65" t="n">
+        <v>-0.477971924387307</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>15</v>
+      </c>
+      <c r="B66" t="s">
+        <v>16</v>
+      </c>
+      <c r="C66" t="n">
+        <v>0.296804386550528</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>15</v>
+      </c>
+      <c r="B67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C67" t="n">
+        <v>-0.550183544037729</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>15</v>
+      </c>
+      <c r="B68" t="s">
+        <v>16</v>
+      </c>
+      <c r="C68" t="n">
+        <v>-0.106806690238967</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>15</v>
+      </c>
+      <c r="B69" t="s">
+        <v>16</v>
+      </c>
+      <c r="C69" t="n">
+        <v>-0.798895944673215</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>15</v>
+      </c>
+      <c r="B70" t="s">
+        <v>16</v>
+      </c>
+      <c r="C70" t="n">
+        <v>-1.2063410142419</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>15</v>
+      </c>
+      <c r="B71" t="s">
+        <v>16</v>
+      </c>
+      <c r="C71" t="n">
+        <v>-1.24579411013015</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>15</v>
+      </c>
+      <c r="B72" t="s">
+        <v>16</v>
+      </c>
+      <c r="C72" t="n">
+        <v>-1.50598867125055</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>15</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="n">
+        <v>-1.40933905695702</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>15</v>
+      </c>
+      <c r="B74" t="s">
+        <v>16</v>
+      </c>
+      <c r="C74" t="n">
+        <v>-1.40368269066049</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>15</v>
+      </c>
+      <c r="B75" t="s">
+        <v>16</v>
+      </c>
+      <c r="C75" t="n">
+        <v>-2.38900966090968</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>15</v>
+      </c>
+      <c r="B76" t="s">
+        <v>16</v>
+      </c>
+      <c r="C76" t="n">
+        <v>-1.44023227732593</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>15</v>
+      </c>
+      <c r="B77" t="s">
+        <v>16</v>
+      </c>
+      <c r="C77" t="n">
+        <v>-0.129894972080633</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>15</v>
+      </c>
+      <c r="B78" t="s">
+        <v>16</v>
+      </c>
+      <c r="C78" t="n">
+        <v>-0.692173638150798</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>15</v>
+      </c>
+      <c r="B79" t="s">
+        <v>16</v>
+      </c>
+      <c r="C79" t="n">
+        <v>-1.20892524753328</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" t="s">
+        <v>16</v>
+      </c>
+      <c r="C80" t="n">
+        <v>-1.30794623482911</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>15</v>
+      </c>
+      <c r="B81" t="s">
+        <v>16</v>
+      </c>
+      <c r="C81" t="n">
+        <v>-0.0913759944152603</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="n">
+        <v>-1.59837662800114</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>15</v>
+      </c>
+      <c r="B83" t="s">
+        <v>16</v>
+      </c>
+      <c r="C83" t="n">
+        <v>0.167224983070419</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>15</v>
+      </c>
+      <c r="B84" t="s">
+        <v>16</v>
+      </c>
+      <c r="C84" t="n">
+        <v>0.373631198199799</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>15</v>
+      </c>
+      <c r="B85" t="s">
+        <v>16</v>
+      </c>
+      <c r="C85" t="n">
+        <v>-1.42697254959035</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>15</v>
+      </c>
+      <c r="B86" t="s">
+        <v>16</v>
+      </c>
+      <c r="C86" t="n">
+        <v>-0.533371623031905</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>15</v>
+      </c>
+      <c r="B87" t="s">
+        <v>16</v>
+      </c>
+      <c r="C87" t="n">
+        <v>-1.47209482367082</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>15</v>
+      </c>
+      <c r="B88" t="s">
+        <v>16</v>
+      </c>
+      <c r="C88" t="n">
+        <v>-1.6530000534538</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>15</v>
+      </c>
+      <c r="B89" t="s">
+        <v>16</v>
+      </c>
+      <c r="C89" t="n">
+        <v>-0.000686620173106389</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>15</v>
+      </c>
+      <c r="B90" t="s">
+        <v>16</v>
+      </c>
+      <c r="C90" t="n">
+        <v>-0.698062263597082</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>15</v>
+      </c>
+      <c r="B91" t="s">
+        <v>16</v>
+      </c>
+      <c r="C91" t="n">
+        <v>-2.10460364161161</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>15</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="n">
+        <v>-0.667573522372553</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s">
+        <v>16</v>
+      </c>
+      <c r="C93" t="n">
+        <v>-1.73236439288726</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>15</v>
+      </c>
+      <c r="B94" t="s">
+        <v>16</v>
+      </c>
+      <c r="C94" t="n">
+        <v>-1.096907085106</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>15</v>
+      </c>
+      <c r="B95" t="s">
+        <v>16</v>
+      </c>
+      <c r="C95" t="n">
+        <v>0.0996238622341626</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>15</v>
+      </c>
+      <c r="B96" t="s">
+        <v>16</v>
+      </c>
+      <c r="C96" t="n">
+        <v>-1.26314867225225</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>15</v>
+      </c>
+      <c r="B97" t="s">
+        <v>16</v>
+      </c>
+      <c r="C97" t="n">
+        <v>0.799192894942245</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>15</v>
+      </c>
+      <c r="B98" t="s">
+        <v>16</v>
+      </c>
+      <c r="C98" t="n">
+        <v>-0.767703047961779</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>15</v>
+      </c>
+      <c r="B99" t="s">
+        <v>16</v>
+      </c>
+      <c r="C99" t="n">
+        <v>-0.469272976354085</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>15</v>
+      </c>
+      <c r="B100" t="s">
+        <v>16</v>
+      </c>
+      <c r="C100" t="n">
+        <v>-1.11361932125271</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>15</v>
+      </c>
+      <c r="B101" t="s">
+        <v>16</v>
+      </c>
+      <c r="C101" t="n">
+        <v>0.388076995024278</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>15</v>
+      </c>
+      <c r="B102" t="s">
+        <v>16</v>
+      </c>
+      <c r="C102" t="n">
+        <v>-0.782028404465299</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>15</v>
+      </c>
+      <c r="B103" t="s">
+        <v>16</v>
+      </c>
+      <c r="C103" t="n">
+        <v>-2.40247067427827</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>15</v>
+      </c>
+      <c r="B104" t="s">
+        <v>16</v>
+      </c>
+      <c r="C104" t="n">
+        <v>-1.71466133627313</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>15</v>
+      </c>
+      <c r="B105" t="s">
+        <v>16</v>
+      </c>
+      <c r="C105" t="n">
+        <v>-0.952366087295537</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>15</v>
+      </c>
+      <c r="B106" t="s">
+        <v>16</v>
+      </c>
+      <c r="C106" t="n">
+        <v>-0.317897783315122</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>15</v>
+      </c>
+      <c r="B107" t="s">
+        <v>16</v>
+      </c>
+      <c r="C107" t="n">
+        <v>-0.805152890925924</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>15</v>
+      </c>
+      <c r="B108" t="s">
+        <v>16</v>
+      </c>
+      <c r="C108" t="n">
+        <v>-0.105206092027949</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>15</v>
+      </c>
+      <c r="B109" t="s">
+        <v>16</v>
+      </c>
+      <c r="C109" t="n">
+        <v>-0.200390212395108</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>15</v>
+      </c>
+      <c r="B110" t="s">
+        <v>16</v>
+      </c>
+      <c r="C110" t="n">
+        <v>-0.713187281585351</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>15</v>
+      </c>
+      <c r="B111" t="s">
+        <v>16</v>
+      </c>
+      <c r="C111" t="n">
+        <v>-0.115817822056317</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>15</v>
+      </c>
+      <c r="B112" t="s">
+        <v>16</v>
+      </c>
+      <c r="C112" t="n">
+        <v>-0.031273565173292</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>15</v>
+      </c>
+      <c r="B113" t="s">
+        <v>16</v>
+      </c>
+      <c r="C113" t="n">
+        <v>-0.656906019117501</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>15</v>
+      </c>
+      <c r="B114" t="s">
+        <v>16</v>
+      </c>
+      <c r="C114" t="n">
+        <v>0.345636691371461</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>15</v>
+      </c>
+      <c r="B115" t="s">
+        <v>16</v>
+      </c>
+      <c r="C115" t="n">
+        <v>0.0661260352384994</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>15</v>
+      </c>
+      <c r="B116" t="s">
+        <v>16</v>
+      </c>
+      <c r="C116" t="n">
+        <v>-1.36512435703836</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>15</v>
+      </c>
+      <c r="B117" t="s">
+        <v>16</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.254925858159896</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>15</v>
+      </c>
+      <c r="B118" t="s">
+        <v>16</v>
+      </c>
+      <c r="C118" t="n">
+        <v>-0.700279692205791</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>15</v>
+      </c>
+      <c r="B119" t="s">
+        <v>16</v>
+      </c>
+      <c r="C119" t="n">
+        <v>-3.41361264992031</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>15</v>
+      </c>
+      <c r="B120" t="s">
+        <v>16</v>
+      </c>
+      <c r="C120" t="n">
+        <v>-1.37822330253789</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>15</v>
+      </c>
+      <c r="B121" t="s">
+        <v>16</v>
+      </c>
+      <c r="C121" t="n">
+        <v>-0.357835170726425</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>15</v>
+      </c>
+      <c r="B122" t="s">
+        <v>16</v>
+      </c>
+      <c r="C122" t="n">
+        <v>-0.134084178286264</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>15</v>
+      </c>
+      <c r="B123" t="s">
+        <v>16</v>
+      </c>
+      <c r="C123" t="n">
+        <v>-2.12804020755746</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>15</v>
+      </c>
+      <c r="B124" t="s">
+        <v>16</v>
+      </c>
+      <c r="C124" t="n">
+        <v>-0.0589815017677198</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>15</v>
+      </c>
+      <c r="B125" t="s">
+        <v>16</v>
+      </c>
+      <c r="C125" t="n">
+        <v>-0.084029534745826</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>15</v>
+      </c>
+      <c r="B126" t="s">
+        <v>16</v>
+      </c>
+      <c r="C126" t="n">
+        <v>-0.628075992792602</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>15</v>
+      </c>
+      <c r="B127" t="s">
+        <v>16</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.0472065382321469</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>15</v>
+      </c>
+      <c r="B128" t="s">
+        <v>16</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.485584308684508</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>15</v>
+      </c>
+      <c r="B129" t="s">
+        <v>16</v>
+      </c>
+      <c r="C129" t="n">
+        <v>-1.61816381387292</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>15</v>
+      </c>
+      <c r="B130" t="s">
+        <v>16</v>
+      </c>
+      <c r="C130" t="n">
+        <v>-1.00786853052383</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>15</v>
+      </c>
+      <c r="B131" t="s">
+        <v>16</v>
+      </c>
+      <c r="C131" t="n">
+        <v>-1.52406940783127</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>15</v>
+      </c>
+      <c r="B132" t="s">
+        <v>16</v>
+      </c>
+      <c r="C132" t="n">
+        <v>-0.390814575416328</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>15</v>
+      </c>
+      <c r="B133" t="s">
+        <v>16</v>
+      </c>
+      <c r="C133" t="n">
+        <v>-0.526431576622385</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>15</v>
+      </c>
+      <c r="B134" t="s">
+        <v>16</v>
+      </c>
+      <c r="C134" t="n">
+        <v>-0.387757264939784</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>15</v>
+      </c>
+      <c r="B135" t="s">
+        <v>16</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.0476761366719507</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>15</v>
+      </c>
+      <c r="B136" t="s">
+        <v>16</v>
+      </c>
+      <c r="C136" t="n">
+        <v>-0.449128553366486</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>15</v>
+      </c>
+      <c r="B137" t="s">
+        <v>16</v>
+      </c>
+      <c r="C137" t="n">
+        <v>-0.824349412420749</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>15</v>
+      </c>
+      <c r="B138" t="s">
+        <v>16</v>
+      </c>
+      <c r="C138" t="n">
+        <v>-1.32669433610181</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>15</v>
+      </c>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="n">
+        <v>-0.486031034045912</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>15</v>
+      </c>
+      <c r="B140" t="s">
+        <v>16</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.213832325262847</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>15</v>
+      </c>
+      <c r="B141" t="s">
+        <v>16</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.00993734586589945</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>15</v>
+      </c>
+      <c r="B142" t="s">
+        <v>16</v>
+      </c>
+      <c r="C142" t="n">
+        <v>-0.312242664615902</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>15</v>
+      </c>
+      <c r="B143" t="s">
+        <v>16</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.275950072680009</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>15</v>
+      </c>
+      <c r="B144" t="s">
+        <v>16</v>
+      </c>
+      <c r="C144" t="n">
+        <v>-2.00612711393187</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>15</v>
+      </c>
+      <c r="B145" t="s">
+        <v>16</v>
+      </c>
+      <c r="C145" t="n">
+        <v>-1.01451156758779</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>15</v>
+      </c>
+      <c r="B146" t="s">
+        <v>16</v>
+      </c>
+      <c r="C146" t="n">
+        <v>-1.23008935407901</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>15</v>
+      </c>
+      <c r="B147" t="s">
+        <v>16</v>
+      </c>
+      <c r="C147" t="n">
+        <v>-0.541960970436744</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>15</v>
+      </c>
+      <c r="B148" t="s">
+        <v>16</v>
+      </c>
+      <c r="C148" t="n">
+        <v>-0.340463425479005</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>15</v>
+      </c>
+      <c r="B149" t="s">
+        <v>16</v>
+      </c>
+      <c r="C149" t="n">
+        <v>-0.0165218389618738</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>15</v>
+      </c>
+      <c r="B150" t="s">
+        <v>16</v>
+      </c>
+      <c r="C150" t="n">
+        <v>-0.58747536376225</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>15</v>
+      </c>
+      <c r="B151" t="s">
+        <v>16</v>
+      </c>
+      <c r="C151" t="n">
+        <v>-0.277358236990866</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>15</v>
+      </c>
+      <c r="B152" t="s">
+        <v>16</v>
+      </c>
+      <c r="C152" t="n">
+        <v>-1.11094346114438</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>15</v>
+      </c>
+      <c r="B153" t="s">
+        <v>16</v>
+      </c>
+      <c r="C153" t="n">
+        <v>-0.114541886907555</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>15</v>
+      </c>
+      <c r="B154" t="s">
+        <v>16</v>
+      </c>
+      <c r="C154" t="n">
+        <v>-1.44225480554903</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>15</v>
+      </c>
+      <c r="B155" t="s">
+        <v>16</v>
+      </c>
+      <c r="C155" t="n">
+        <v>-0.83874126574134</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>15</v>
+      </c>
+      <c r="B156" t="s">
+        <v>16</v>
+      </c>
+      <c r="C156" t="n">
+        <v>-0.890017075260779</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>15</v>
+      </c>
+      <c r="B157" t="s">
+        <v>16</v>
+      </c>
+      <c r="C157" t="n">
+        <v>-0.744326379919761</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>15</v>
+      </c>
+      <c r="B158" t="s">
+        <v>16</v>
+      </c>
+      <c r="C158" t="n">
+        <v>-0.175657854001834</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>15</v>
+      </c>
+      <c r="B159" t="s">
+        <v>16</v>
+      </c>
+      <c r="C159" t="n">
+        <v>-0.37693086392579</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>15</v>
+      </c>
+      <c r="B160" t="s">
+        <v>16</v>
+      </c>
+      <c r="C160" t="n">
+        <v>-1.38244558738863</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>15</v>
+      </c>
+      <c r="B161" t="s">
+        <v>16</v>
+      </c>
+      <c r="C161" t="n">
+        <v>-0.494713453502633</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>15</v>
+      </c>
+      <c r="B162" t="s">
+        <v>16</v>
+      </c>
+      <c r="C162" t="n">
+        <v>-2.0903412251466</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>15</v>
+      </c>
+      <c r="B163" t="s">
+        <v>16</v>
+      </c>
+      <c r="C163" t="n">
+        <v>-2.72786992435028</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>15</v>
+      </c>
+      <c r="B164" t="s">
+        <v>16</v>
+      </c>
+      <c r="C164" t="n">
+        <v>-0.630292969089824</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>15</v>
+      </c>
+      <c r="B165" t="s">
+        <v>16</v>
+      </c>
+      <c r="C165" t="n">
+        <v>0.0219067073687386</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>15</v>
+      </c>
+      <c r="B166" t="s">
+        <v>16</v>
+      </c>
+      <c r="C166" t="n">
+        <v>-0.622999999333926</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>15</v>
+      </c>
+      <c r="B167" t="s">
+        <v>16</v>
+      </c>
+      <c r="C167" t="n">
+        <v>-1.40378913952903</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>15</v>
+      </c>
+      <c r="B168" t="s">
+        <v>16</v>
+      </c>
+      <c r="C168" t="n">
+        <v>0.455941192489054</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>15</v>
+      </c>
+      <c r="B169" t="s">
+        <v>16</v>
+      </c>
+      <c r="C169" t="n">
+        <v>0.132400782564435</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>15</v>
+      </c>
+      <c r="B170" t="s">
+        <v>16</v>
+      </c>
+      <c r="C170" t="n">
+        <v>-0.493687172907875</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>15</v>
+      </c>
+      <c r="B171" t="s">
+        <v>16</v>
+      </c>
+      <c r="C171" t="n">
+        <v>-0.0735224040746953</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>15</v>
+      </c>
+      <c r="B172" t="s">
+        <v>16</v>
+      </c>
+      <c r="C172" t="n">
+        <v>-0.605859909495198</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>15</v>
+      </c>
+      <c r="B173" t="s">
+        <v>16</v>
+      </c>
+      <c r="C173" t="n">
+        <v>-0.0610991875811664</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>15</v>
+      </c>
+      <c r="B174" t="s">
+        <v>16</v>
+      </c>
+      <c r="C174" t="n">
+        <v>0.0409485425276818</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>15</v>
+      </c>
+      <c r="B175" t="s">
+        <v>16</v>
+      </c>
+      <c r="C175" t="n">
+        <v>0.349913152516386</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>15</v>
+      </c>
+      <c r="B176" t="s">
+        <v>16</v>
+      </c>
+      <c r="C176" t="n">
+        <v>-0.24100736186971</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>15</v>
+      </c>
+      <c r="B177" t="s">
+        <v>16</v>
+      </c>
+      <c r="C177" t="n">
+        <v>-0.924124111482145</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>15</v>
+      </c>
+      <c r="B178" t="s">
+        <v>16</v>
+      </c>
+      <c r="C178" t="n">
+        <v>0.225075119617509</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>15</v>
+      </c>
+      <c r="B179" t="s">
+        <v>16</v>
+      </c>
+      <c r="C179" t="n">
+        <v>-0.184409776821572</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>15</v>
+      </c>
+      <c r="B180" t="s">
+        <v>16</v>
+      </c>
+      <c r="C180" t="n">
+        <v>0.27982569500326</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>15</v>
+      </c>
+      <c r="B181" t="s">
+        <v>16</v>
+      </c>
+      <c r="C181" t="n">
+        <v>-0.170361932355318</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>15</v>
+      </c>
+      <c r="B182" t="s">
+        <v>16</v>
+      </c>
+      <c r="C182" t="n">
+        <v>-0.175685096774123</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>15</v>
+      </c>
+      <c r="B183" t="s">
+        <v>16</v>
+      </c>
+      <c r="C183" t="n">
+        <v>0.0112612526216097</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>15</v>
+      </c>
+      <c r="B184" t="s">
+        <v>16</v>
+      </c>
+      <c r="C184" t="n">
+        <v>-1.09689326068733</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>15</v>
+      </c>
+      <c r="B185" t="s">
+        <v>16</v>
+      </c>
+      <c r="C185" t="n">
+        <v>0.711466976556128</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>15</v>
+      </c>
+      <c r="B186" t="s">
+        <v>16</v>
+      </c>
+      <c r="C186" t="n">
+        <v>-0.301143413547199</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>16</v>
+      </c>
+      <c r="C187" t="n">
+        <v>-1.91115412059429</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>15</v>
+      </c>
+      <c r="B188" t="s">
+        <v>16</v>
+      </c>
+      <c r="C188" t="n">
+        <v>-0.87198274059526</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>15</v>
+      </c>
+      <c r="B189" t="s">
+        <v>16</v>
+      </c>
+      <c r="C189" t="n">
+        <v>0.211846279858519</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>15</v>
+      </c>
+      <c r="B190" t="s">
+        <v>16</v>
+      </c>
+      <c r="C190" t="n">
+        <v>-0.692018999542506</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>15</v>
+      </c>
+      <c r="B191" t="s">
+        <v>16</v>
+      </c>
+      <c r="C191" t="n">
+        <v>-2.07393331237371</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>15</v>
+      </c>
+      <c r="B192" t="s">
+        <v>16</v>
+      </c>
+      <c r="C192" t="n">
+        <v>-1.07040730416397</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>15</v>
+      </c>
+      <c r="B193" t="s">
+        <v>16</v>
+      </c>
+      <c r="C193" t="n">
+        <v>-0.917003255091573</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>15</v>
+      </c>
+      <c r="B194" t="s">
+        <v>16</v>
+      </c>
+      <c r="C194" t="n">
+        <v>-0.57552450544912</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>15</v>
+      </c>
+      <c r="B195" t="s">
+        <v>16</v>
+      </c>
+      <c r="C195" t="n">
+        <v>-0.599446380432257</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>15</v>
+      </c>
+      <c r="B196" t="s">
+        <v>16</v>
+      </c>
+      <c r="C196" t="n">
+        <v>-0.407863936984926</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>15</v>
+      </c>
+      <c r="B197" t="s">
+        <v>16</v>
+      </c>
+      <c r="C197" t="n">
+        <v>-0.642365222347091</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>15</v>
+      </c>
+      <c r="B198" t="s">
+        <v>16</v>
+      </c>
+      <c r="C198" t="n">
+        <v>-0.595672666408497</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>15</v>
+      </c>
+      <c r="B199" t="s">
+        <v>16</v>
+      </c>
+      <c r="C199" t="n">
+        <v>-2.39906677745743</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>15</v>
+      </c>
+      <c r="B200" t="s">
+        <v>16</v>
+      </c>
+      <c r="C200" t="n">
+        <v>-0.767519663255502</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>15</v>
+      </c>
+      <c r="B201" t="s">
+        <v>16</v>
+      </c>
+      <c r="C201" t="n">
+        <v>-2.05445473304081</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
